--- a/sediment pteropod 13C and 18O data copy.xlsx
+++ b/sediment pteropod 13C and 18O data copy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/clairesheppard/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB985B29-B0EC-9C43-B2FD-EB2C0C625930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0D56FF-C24B-5647-B78C-F2F07C9194FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="1760" windowWidth="27240" windowHeight="16240" activeTab="1" xr2:uid="{5426609D-28EC-8C45-AD40-7F8D452BB8DD}"/>
   </bookViews>
@@ -163,23 +163,23 @@
     <t xml:space="preserve">temp (C°) </t>
   </si>
   <si>
-    <t>Sonic</t>
-  </si>
-  <si>
-    <t>No clean</t>
-  </si>
-  <si>
-    <t>Sonic+red</t>
-  </si>
-  <si>
-    <t>Sonic +red+ox</t>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>SON</t>
+  </si>
+  <si>
+    <t>SON-RED</t>
+  </si>
+  <si>
+    <t>SON-RED-OX</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -310,6 +310,20 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -656,10 +670,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1121,8 +1137,8 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" t="s">
-        <v>43</v>
+      <c r="C4" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="D4">
         <v>110</v>
@@ -1183,8 +1199,8 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
-        <v>43</v>
+      <c r="C5" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="D5">
         <v>110</v>
@@ -1245,8 +1261,8 @@
       <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" t="s">
-        <v>43</v>
+      <c r="C6" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="D6">
         <v>111</v>
@@ -1307,8 +1323,8 @@
       <c r="B7">
         <v>2</v>
       </c>
-      <c r="C7" t="s">
-        <v>42</v>
+      <c r="C7" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="D7">
         <v>278</v>
@@ -1369,8 +1385,8 @@
       <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" t="s">
-        <v>42</v>
+      <c r="C8" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="D8">
         <v>277</v>
@@ -1431,8 +1447,8 @@
       <c r="B9">
         <v>2</v>
       </c>
-      <c r="C9" t="s">
-        <v>42</v>
+      <c r="C9" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="D9">
         <v>281</v>
@@ -1493,7 +1509,7 @@
       <c r="B10">
         <v>3</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D10">
@@ -1555,7 +1571,7 @@
       <c r="B11">
         <v>3</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D11">
@@ -1617,7 +1633,7 @@
       <c r="B12">
         <v>3</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="4" t="s">
         <v>44</v>
       </c>
       <c r="D12">
@@ -1679,7 +1695,7 @@
       <c r="B13">
         <v>4</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D13">
@@ -1741,7 +1757,7 @@
       <c r="B14">
         <v>4</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D14">
@@ -1803,7 +1819,7 @@
       <c r="B15">
         <v>4</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D15">
@@ -1928,8 +1944,8 @@
       <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>43</v>
+      <c r="B2" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="C2">
         <v>1.3</v>
@@ -1973,8 +1989,8 @@
       <c r="A3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" t="s">
-        <v>43</v>
+      <c r="B3" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="C3">
         <v>1.54</v>
@@ -2018,8 +2034,8 @@
       <c r="A4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" t="s">
-        <v>43</v>
+      <c r="B4" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="C4">
         <v>1.45</v>
@@ -2063,8 +2079,8 @@
       <c r="A5" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
-        <v>42</v>
+      <c r="B5" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="C5">
         <v>1.1200000000000001</v>
@@ -2108,8 +2124,8 @@
       <c r="A6" t="s">
         <v>28</v>
       </c>
-      <c r="B6" t="s">
-        <v>42</v>
+      <c r="B6" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="C6">
         <v>1.23</v>
@@ -2153,8 +2169,8 @@
       <c r="A7" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
-        <v>42</v>
+      <c r="B7" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="C7">
         <v>1.58</v>
@@ -2198,7 +2214,7 @@
       <c r="A8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C8">
@@ -2243,7 +2259,7 @@
       <c r="A9" t="s">
         <v>31</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C9">
@@ -2288,7 +2304,7 @@
       <c r="A10" t="s">
         <v>32</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C10">
@@ -2333,7 +2349,7 @@
       <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C11">
@@ -2378,7 +2394,7 @@
       <c r="A12" t="s">
         <v>34</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C12">
@@ -2423,7 +2439,7 @@
       <c r="A13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C13">

--- a/sediment pteropod 13C and 18O data copy.xlsx
+++ b/sediment pteropod 13C and 18O data copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/clairesheppard/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF0D56FF-C24B-5647-B78C-F2F07C9194FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDABB2BA-DFC5-9747-92F0-A6AC40F646AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="1760" windowWidth="27240" windowHeight="16240" activeTab="1" xr2:uid="{5426609D-28EC-8C45-AD40-7F8D452BB8DD}"/>
+    <workbookView xWindow="540" yWindow="1500" windowWidth="22120" windowHeight="16240" activeTab="1" xr2:uid="{5426609D-28EC-8C45-AD40-7F8D452BB8DD}"/>
   </bookViews>
   <sheets>
     <sheet name="OCE205-2-60BC_all+data(all+data" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="46">
   <si>
     <t>SAMPLE PREPARATION</t>
   </si>
@@ -1890,13 +1890,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4CAE81A-D763-844E-9B78-DADD39A924BD}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -1939,8 +1939,11 @@
       <c r="N1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -1984,8 +1987,11 @@
       <c r="N2">
         <v>1312</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O2" s="2">
+        <v>3670</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -2029,8 +2035,11 @@
       <c r="N3">
         <v>1312</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O3" s="2">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -2074,8 +2083,11 @@
       <c r="N4">
         <v>1312</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O4" s="2">
+        <v>3910</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -2119,8 +2131,11 @@
       <c r="N5">
         <v>1312</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O5" s="2">
+        <v>3560</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -2164,8 +2179,11 @@
       <c r="N6">
         <v>1312</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O6" s="2">
+        <v>3660</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -2209,8 +2227,11 @@
       <c r="N7">
         <v>1312</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2">
+        <v>3910</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -2254,8 +2275,11 @@
       <c r="N8">
         <v>1312</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8">
+        <v>3530</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -2299,8 +2323,11 @@
       <c r="N9">
         <v>1312</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9">
+        <v>3580</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -2344,8 +2371,11 @@
       <c r="N10">
         <v>1312</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -2389,8 +2419,11 @@
       <c r="N11">
         <v>1312</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11">
+        <v>3690</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -2434,8 +2467,11 @@
       <c r="N12">
         <v>1312</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -2478,6 +2514,9 @@
       </c>
       <c r="N13">
         <v>1312</v>
+      </c>
+      <c r="O13">
+        <v>3560</v>
       </c>
     </row>
   </sheetData>
